--- a/OpenSesame-local/Messages.xlsx
+++ b/OpenSesame-local/Messages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cdabb12e9f34f4c5/10_Paper/105_MIA/10_BAS_Collab/MBRT/OpenSesame-local/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{2A0343A6-2272-4E3D-9015-9F132571742E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B66F3B1A-3B4A-47AE-ACD6-233AEE0A7D97}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="13_ncr:1_{2A0343A6-2272-4E3D-9015-9F132571742E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE7B6ED3-4BD5-4D83-A135-CB2389DCE69A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38078" yWindow="720" windowWidth="26084" windowHeight="13829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -96,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>EN</t>
   </si>
@@ -141,6 +144,36 @@
   </si>
   <si>
     <t>Willkommen zum Experiment!</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>¡Bienvenido al experimento!</t>
+  </si>
+  <si>
+    <t>Bienvenue dans l’expérience !</t>
+  </si>
+  <si>
+    <t>Por favor, utilice las siguientes teclas:</t>
+  </si>
+  <si>
+    <t>Veuillez utiliser les touches suivantes :</t>
+  </si>
+  <si>
+    <t>Presiona ESPACIO para continuar</t>
+  </si>
+  <si>
+    <t>Appuyez sur ESPACE pour continuer</t>
+  </si>
+  <si>
+    <t>Este es el final del experimento.&lt;br&gt;&lt;br&gt;&lt;b&gt;¡Gracias por participar!&lt;br&gt;&lt;br&gt;&lt;b&gt;Espera 3 segundos para salir</t>
+  </si>
+  <si>
+    <t>Ceci est la fin de l'expérience.&lt;br&gt;&lt;br&gt;&lt;b&gt;Merci d'avoir participé !&lt;br&gt;&lt;br&gt;&lt;b&gt;Attendez 3 secondes pour quitter</t>
   </si>
 </sst>
 </file>
@@ -205,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -216,8 +249,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -244,9 +281,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 – 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -284,7 +321,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 – 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -390,7 +427,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 – 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -532,7 +569,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -540,67 +577,99 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="20.7109375" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="20.75" defaultRowHeight="20.05" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="40.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="12.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="92.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="114.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="91.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="94" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="14.3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:5" ht="14.3" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:5" ht="14.3" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="D3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:5" ht="14.3" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="D4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:5" ht="14.3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>9</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -616,12 +685,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B9F5CAB0486A994CA2C3B13E059EF2AE" ma:contentTypeVersion="0" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8645ec4a60d0c8c7009d2d6675847a91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="636d7205651659ec4fcda0bcbde9384b">
     <xsd:element name="properties">
@@ -735,6 +798,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -745,21 +814,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF1C174-6AC6-4774-A736-3226A12360E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -775,6 +829,21 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
   <ds:schemaRefs>
